--- a/employee_leave_records.xlsx
+++ b/employee_leave_records.xlsx
@@ -59,6 +59,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$Rs]#,##0.00"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="10.0"/>
@@ -86,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -94,6 +97,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -363,10 +369,10 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="3">
         <v>15.0</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="3">
         <v>200.0</v>
       </c>
     </row>
@@ -389,10 +395,10 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="3">
         <v>10.0</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="3">
         <v>100.0</v>
       </c>
     </row>
